--- a/Result/profitability/1313.xlsx
+++ b/Result/profitability/1313.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.175</v>
+        <v>-0.07750000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>2.59375</v>
+        <v>3.635</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03625</v>
+        <v>0.02124999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7325</v>
+        <v>4.25375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0325</v>
+        <v>0.08624999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>4.18125</v>
+        <v>4.65625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.27</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.10125</v>
+        <v>-0.05875000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.80625</v>
+        <v>-1.275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0675</v>
+        <v>-0.00750000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0275</v>
+        <v>-0.3000000000000003</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01499999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2150000000000001</v>
+        <v>0.8637499999999998</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1675</v>
+        <v>0.18625</v>
       </c>
       <c r="N8" t="n">
-        <v>1.19125</v>
+        <v>1.2625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16636</v>
+      </c>
+      <c r="D75" t="n">
+        <v>15508</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>433</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-46</v>
+      </c>
+      <c r="J75" t="n">
+        <v>387</v>
+      </c>
+      <c r="K75" t="n">
+        <v>313</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2.76375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5700000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09178743961352653</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.090909090909091</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.679841897233202</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
